--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20250401_20251001.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20250401_20251001.xlsx
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
         <v>-16.12903225806452</v>
@@ -728,7 +728,7 @@
         <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7" t="n">
         <v>2584.4</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
         <v>-16.12903225806452</v>
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J8" t="n">
         <v>7286</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
         <v>-15.3225806451613</v>
@@ -816,7 +816,7 @@
         <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J9" t="n">
         <v>329.44</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
         <v>-12.90322580645162</v>
@@ -904,7 +904,7 @@
         <v>23</v>
       </c>
       <c r="I11" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J11" t="n">
         <v>5472.5</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
         <v>-19.35483870967742</v>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J13" t="n">
         <v>1575.9</v>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
         <v>-12.90322580645162</v>
@@ -1036,7 +1036,7 @@
         <v>26</v>
       </c>
       <c r="I14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J14" t="n">
         <v>974.6</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
         <v>-16.12903225806452</v>
@@ -1168,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J17" t="n">
         <v>841.8</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
         <v>-12.90322580645162</v>
@@ -1256,7 +1256,7 @@
         <v>22</v>
       </c>
       <c r="I19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J19" t="n">
         <v>813.6</v>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
         <v>-9.677419354838712</v>
@@ -1344,7 +1344,7 @@
         <v>45</v>
       </c>
       <c r="I21" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J21" t="n">
         <v>2826.8</v>
